--- a/data/trans_orig/IP2005-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39281</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>45272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>49787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84178</t>
+          <t>84533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94192</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72038</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>83360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>80255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>92754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156070</t>
+          <t>156076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172961</t>
+          <t>172645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>43032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57797</t>
+          <t>57790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62612</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>126053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>63710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>69594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69405</t>
+          <t>69416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75539</t>
+          <t>75548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136327</t>
+          <t>135893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143822</t>
+          <t>143803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>71694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46611</t>
+          <t>46445</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52135</t>
+          <t>52119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101799</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108616</t>
+          <t>108612</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102725</t>
+          <t>103481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114131</t>
+          <t>114198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106546</t>
+          <t>106871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117625</t>
+          <t>117573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213032</t>
+          <t>212381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229139</t>
+          <t>229264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116509</t>
+          <t>116325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130515</t>
+          <t>130450</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120550</t>
+          <t>119805</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135349</t>
+          <t>135591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242173</t>
+          <t>242400</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>262432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>38968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59227</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>552531</t>
+          <t>550920</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>576424</t>
+          <t>577113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>588262</t>
+          <t>588853</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>613949</t>
+          <t>615466</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1148769</t>
+          <t>1147811</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1184449</t>
+          <t>1183551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83507</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64316</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>89412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129854</t>
+          <t>130752</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>165534</t>
+          <t>166492</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>42489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>51461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55968</t>
+          <t>55785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>94724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105604</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>80185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89990</t>
+          <t>90206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81036</t>
+          <t>81535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93220</t>
+          <t>92683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165660</t>
+          <t>165762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179854</t>
+          <t>180997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53725</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>60674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>60889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>65784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117484</t>
+          <t>117097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125625</t>
+          <t>125822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>63620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73242</t>
+          <t>73205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123344</t>
+          <t>125063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137451</t>
+          <t>138489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30460</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>43071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>69220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79953</t>
+          <t>80564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>42068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47857</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40746</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50568</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85576</t>
+          <t>85433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97600</t>
+          <t>97112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110692</t>
+          <t>111161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121902</t>
+          <t>122128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117471</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>126897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232092</t>
+          <t>232835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246905</t>
+          <t>246809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136627</t>
+          <t>136572</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148055</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>144333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156036</t>
+          <t>156057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>285026</t>
+          <t>285388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>300888</t>
+          <t>301148</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36536</t>
+          <t>36174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>582311</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>608271</t>
+          <t>607939</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>622104</t>
+          <t>622114</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>647771</t>
+          <t>647513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1212613</t>
+          <t>1213770</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1249917</t>
+          <t>1248925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>77781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>77479</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>110982</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147294</t>
+          <t>146137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>53463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109363</t>
+          <t>109776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115908</t>
+          <t>115910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90293</t>
+          <t>89436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96135</t>
+          <t>95919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>86807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>98279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180900</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193104</t>
+          <t>192758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>60375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59224</t>
+          <t>59858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117207</t>
+          <t>117288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125480</t>
+          <t>125481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60623</t>
+          <t>60339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69246</t>
+          <t>68997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60637</t>
+          <t>60477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70847</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125862</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138768</t>
+          <t>138135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28989</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63986</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>49643</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95934</t>
+          <t>96289</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103594</t>
+          <t>103606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118808</t>
+          <t>119226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127129</t>
+          <t>127083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119453</t>
+          <t>118879</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129174</t>
+          <t>129130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241347</t>
+          <t>241700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253897</t>
+          <t>254363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>123815</t>
+          <t>123121</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136145</t>
+          <t>136246</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133708</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>147023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259796</t>
+          <t>261461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>279781</t>
+          <t>279848</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>27879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47931</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>621850</t>
+          <t>621485</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>622476</t>
+          <t>623220</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>648463</t>
+          <t>648223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1231855</t>
+          <t>1229970</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1266165</t>
+          <t>1263683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75676</t>
+          <t>74932</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67212</t>
+          <t>68192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>72416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76432</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141465</t>
+          <t>141079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148030</t>
+          <t>148131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99971</t>
+          <t>100585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117083</t>
+          <t>118422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89209</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107628</t>
+          <t>107508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196019</t>
+          <t>193745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222938</t>
+          <t>222656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44453</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>49239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>60099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111067</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42945</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67972</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100455</t>
+          <t>101747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121764</t>
+          <t>122671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>29229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34269</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65957</t>
+          <t>66145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>72284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42067</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48723</t>
+          <t>48333</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>53594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86872</t>
+          <t>86791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94830</t>
+          <t>94857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98053</t>
+          <t>97301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111072</t>
+          <t>110695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115625</t>
+          <t>116217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135035</t>
+          <t>134818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218035</t>
+          <t>219156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>242637</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>38640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60400</t>
+          <t>59279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113214</t>
+          <t>113763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123662</t>
+          <t>123911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144219</t>
+          <t>144449</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152160</t>
+          <t>152192</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>261288</t>
+          <t>261151</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274067</t>
+          <t>274178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561306</t>
+          <t>561769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>591304</t>
+          <t>591434</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>638014</t>
+          <t>638033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>673197</t>
+          <t>672062</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1209241</t>
+          <t>1212458</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1254989</t>
+          <t>1257706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>74697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>108726</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>145569</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>194034</t>
+          <t>190817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
